--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:48</t>
+    <t xml:space="preserve">2026-09-09 22:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:35</t>
+    <t xml:space="preserve">2026-09-12 19:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_atacama.xlsx
@@ -39,30 +39,30 @@
     <t xml:space="preserve">Freirina</t>
   </si>
   <si>
+    <t xml:space="preserve">Caldera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huasco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alto del Carmen</t>
   </si>
   <si>
-    <t xml:space="preserve">Caldera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Huasco</t>
+    <t xml:space="preserve">Chañaral</t>
   </si>
   <si>
     <t xml:space="preserve">Vallenar</t>
   </si>
   <si>
-    <t xml:space="preserve">Chañaral</t>
-  </si>
-  <si>
     <t xml:space="preserve">Copiapó</t>
   </si>
   <si>
+    <t xml:space="preserve">Diego de Almagro</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tierra Amarilla</t>
   </si>
   <si>
-    <t xml:space="preserve">Diego de Almagro</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:51</t>
+    <t xml:space="preserve">2026-09-24 00:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -508,7 +508,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7.72</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="3">
@@ -519,13 +519,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3302</v>
+        <v>3102</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>7.08</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="4">
@@ -536,13 +536,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3102</v>
+        <v>3304</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>6.82</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="5">
@@ -553,13 +553,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3304</v>
+        <v>3302</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.16</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="6">
@@ -570,13 +570,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3301</v>
+        <v>3201</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="7">
@@ -587,13 +587,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>3201</v>
+        <v>3301</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-1.92</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="8">
@@ -610,7 +610,7 @@
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-2.79</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="9">
@@ -621,13 +621,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3103</v>
+        <v>3202</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-8.58</v>
+        <v>-3.52</v>
       </c>
     </row>
     <row r="10">
@@ -638,13 +638,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>3202</v>
+        <v>3103</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-10.22</v>
+        <v>-3.94</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:30</t>
+    <t xml:space="preserve">2026-09-27 23:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -508,7 +508,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>3.54</v>
+        <v>35.42</v>
       </c>
     </row>
     <row r="3">
@@ -525,7 +525,7 @@
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2.25</v>
+        <v>22.52</v>
       </c>
     </row>
     <row r="4">
@@ -542,7 +542,7 @@
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1.57</v>
+        <v>15.66</v>
       </c>
     </row>
     <row r="5">
@@ -559,7 +559,7 @@
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.96</v>
+        <v>9.65</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.75</v>
+        <v>7.53</v>
       </c>
     </row>
     <row r="7">
@@ -593,7 +593,7 @@
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.19</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="8">
@@ -610,7 +610,7 @@
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.62</v>
+        <v>-6.2</v>
       </c>
     </row>
     <row r="9">
@@ -627,7 +627,7 @@
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-3.52</v>
+        <v>-35.2</v>
       </c>
     </row>
     <row r="10">
@@ -644,7 +644,7 @@
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-3.94</v>
+        <v>-39.43</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:12</t>
+    <t xml:space="preserve">2026-10-01 20:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:58</t>
+    <t xml:space="preserve">2026-10-02 13:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:26</t>
+    <t xml:space="preserve">2026-10-05 08:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
